--- a/test2.xlsx
+++ b/test2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\testscript\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\effective-rotary-phone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2348B60E-78A3-42F2-9885-C904E9B81B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C060EE43-E037-40F0-A4D4-39ADFFA5A5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
+    <workbookView xWindow="5760" yWindow="1275" windowWidth="17565" windowHeight="11475" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>При вызове указал неправильное количество аргументов</t>
   </si>
@@ -61,6 +61,41 @@
     return min(max_by_bodies, max_by_steering, max_by_wheels)
 cars = count_cars(int(input()), int(input()), int(input()))
 print(cars)</t>
+  </si>
+  <si>
+    <t>spruce(6)</t>
+  </si>
+  <si>
+    <t>выведет ошибку</t>
+  </si>
+  <si>
+    <t>m = int(input())
+cm = int(input())
+print(m * 1000 + cm * 10)</t>
+  </si>
+  <si>
+    <t>аргумент</t>
+  </si>
+  <si>
+    <t>ошибка</t>
+  </si>
+  <si>
+    <t>Ничего</t>
+  </si>
+  <si>
+    <t>def, for</t>
+  </si>
+  <si>
+    <t>L = [12, 45, 67, 23, 89, 56, 34, 78, 90, 9, 11, 88, 37, 72, 5, 61, 18, 83, 29, 94, 40, 77, 6, 50, 14, 98, 27, 71, 35, 21, 68, 44, 82, 10, 53, 75, 91, 3, 17, 46, 63, 80, 22, 55, 96, 7, 31, 58, 84]
+def sum(list):
+  sm = 0
+  for i in list:
+    sm+=i
+  return sm
+print(sum(L))</t>
+  </si>
+  <si>
+    <t>and</t>
   </si>
 </sst>
 </file>
@@ -104,7 +139,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -120,9 +155,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -160,7 +195,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -266,7 +301,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -408,7 +443,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -416,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D00819F-1C48-4D61-BB16-78A968D2A3F3}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="55.42578125" customWidth="1"/>
@@ -532,6 +567,116 @@
         <v>5</v>
       </c>
     </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>11860</v>
+      </c>
+      <c r="B11">
+        <v>1167871</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11860</v>
+      </c>
+      <c r="B12">
+        <v>1167872</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11860</v>
+      </c>
+      <c r="B13">
+        <v>1167873</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>11860</v>
+      </c>
+      <c r="B14">
+        <v>1167874</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>11860</v>
+      </c>
+      <c r="B15">
+        <v>1197293</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>11861</v>
+      </c>
+      <c r="B16">
+        <v>1167879</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>11861</v>
+      </c>
+      <c r="B17">
+        <v>1167880</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>11861</v>
+      </c>
+      <c r="B18">
+        <v>1167881</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>11861</v>
+      </c>
+      <c r="B19">
+        <v>1167882</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>11861</v>
+      </c>
+      <c r="B20">
+        <v>1197294</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test2.xlsx
+++ b/test2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\effective-rotary-phone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C060EE43-E037-40F0-A4D4-39ADFFA5A5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4469012-EBF3-448A-8BE8-A2D01F7DC603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="1275" windowWidth="17565" windowHeight="11475" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
+    <workbookView xWindow="6405" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>При вызове указал неправильное количество аргументов</t>
   </si>
@@ -96,6 +96,122 @@
   </si>
   <si>
     <t>and</t>
+  </si>
+  <si>
+    <t>Завершает работу функции, Может быть несколько в одной функции</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>return n</t>
+  </si>
+  <si>
+    <t>def nums(a, b):
+    if a &gt; b:
+        return a * b
+    else:
+        return a + b
+a = int(input())
+b = int(input())
+print(nums(a, b))</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>def cars(bodies, steering_wheels, wheels):
+    return min(bodies, steering_wheels, wheels // 6)
+bodies = int(input())
+steering_wheels = int(input())
+wheels = int(input())
+print(cars(bodies, steering_wheels, wheels))</t>
+  </si>
+  <si>
+    <t>command</t>
+  </si>
+  <si>
+    <t>curl ^"https://kb.cifrium.ru/api/lessons/11863/tasks/1167887/answer_attempts^" ^
+  -H ^"Accept: application/json, text/plain, */*^" ^
+  -H ^"Accept-Language: ru-RU,ru;q=0.9,en-US;q=0.8,en;q=0.7^" ^
+  -H ^"Connection: keep-alive^" ^
+  -H ^"Content-Type: multipart/form-data; boundary=----WebKitFormBoundary1LSBtkPXf0NA7AmQ^" ^
+  -b ^"user_agent_uid=284af99d-2e4a-442c-a69b-28664ccd60d3; mindboxDeviceUUID=9ef4685d-4442-42ec-850a-536d6c39d684; directCrm-session=^%^7B^%^22deviceGuid^%^22^%^3A^%^229ef4685d-4442-42ec-850a-536d6c39d684^%^22^%^7D; _ym_uid=177373422273580916; _ym_d=1773734222; _ym_isad=2; client_timezone=Europe/Moscow; remember_user_token=eyJfcmFpbHMiOnsibWVzc2FnZSI6IlcxczNOakV3TmpCZExDSWtNbUVrTVRBa1ZXMXhWbXN3V2tWcVlYcFNMa3hFT0M4M1FXMVFkU0lzSWpFM056TTNNelF5TnpNdU5EWTBNakV3TXlKZCIsImV4cCI6IjIwMjYtMDYtMTdUMDc6NTc6NTNaIiwicHVyIjpudWxsfX0^%^3D--518159f327e5bc0659cb3bf8a06771a3b9d07c0f; _wk_kbc_session=02489b5608a4cade3d082017601ee9a7; _mkra_stck=pg^%^3A1773735248.7303872; _csrf_token=IG8^%^2FLKq5uCTbOYyLbU2XWQE^%^2F9^%^2F^%^2B9wB9hPv9gj4clq0YGSuEpEWaKGU3Cgh1q9iTFKTGjUgSDj^%^2FGzlXYFkOCdEw^%^3D^%^3D^" ^
+  -H ^"Origin: https://kb.cifrium.ru^" ^
+  -H ^"Referer: https://kb.cifrium.ru/lessons/11863/tasks/1167887^" ^
+  -H ^"Sec-Fetch-Dest: empty^" ^
+  -H ^"Sec-Fetch-Mode: cors^" ^
+  -H ^"Sec-Fetch-Site: same-origin^" ^
+  -H ^"User-Agent: Mozilla/5.0 (Windows NT 10.0; Win64; x64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/145.0.0.0 Safari/537.36^" ^
+  -H ^"X-CSRF-Token: IG8/LKq5uCTbOYyLbU2XWQE/9/+9wB9hPv9gj4clq0YGSuEpEWaKGU3Cgh1q9iTFKTGjUgSDj/GzlXYFkOCdEw==^" ^
+  -H ^"X-Device-Id: fc843a63c432edc43ad8b96dd2c8eae4^" ^
+  -H ^"X-Referer: https://kb.cifrium.ru/lessons/11863/tasks/1167887^" ^
+  -H ^"X-Requested-With: XMLHttpRequest^" ^
+  -H ^"X-Skip-Error-Notification: true^" ^
+  -H ^"sec-ch-ua: ^\^"Not:A-Brand^\^";v=^\^"99^\^", ^\^"Google Chrome^\^";v=^\^"145^\^", ^\^"Chromium^\^";v=^\^"145^\^"^" ^
+  -H ^"sec-ch-ua-mobile: ?0^" ^
+  -H ^"sec-ch-ua-platform: ^\^"Windows^\^"^" ^
+  --data-raw ^"------WebKitFormBoundary1LSBtkPXf0NA7AmQ^
+Content-Disposition: form-data; name=^\^"questions^[1207774^]^[10162110^]^\^"^
+^
+10162111^
+------WebKitFormBoundary1LSBtkPXf0NA7AmQ^
+Content-Disposition: form-data; name=^\^"questions^[1207774^]^[10162112^]^\^"^
+^
+10162113^
+------WebKitFormBoundary1LSBtkPXf0NA7AmQ^
+Content-Disposition: form-data; name=^\^"questions^[1207774^]^[10162114^]^\^"^
+^
+10162115^
+------WebKitFormBoundary1LSBtkPXf0NA7AmQ--^
+^"</t>
+  </si>
+  <si>
+    <t>curl ^"https://kb.cifrium.ru/api/lessons/11863/tasks/1167888/answer_attempts^" ^
+  -H ^"Accept: application/json, text/plain, */*^" ^
+  -H ^"Accept-Language: ru-RU,ru;q=0.9,en-US;q=0.8,en;q=0.7^" ^
+  -H ^"Connection: keep-alive^" ^
+  -H ^"Content-Type: multipart/form-data; boundary=----WebKitFormBoundaryOSVeRHNFQJBW6Cq6^" ^
+  -b ^"user_agent_uid=284af99d-2e4a-442c-a69b-28664ccd60d3; mindboxDeviceUUID=9ef4685d-4442-42ec-850a-536d6c39d684; directCrm-session=^%^7B^%^22deviceGuid^%^22^%^3A^%^229ef4685d-4442-42ec-850a-536d6c39d684^%^22^%^7D; _ym_uid=177373422273580916; _ym_d=1773734222; _ym_isad=2; client_timezone=Europe/Moscow; remember_user_token=eyJfcmFpbHMiOnsibWVzc2FnZSI6IlcxczNOakV3TmpCZExDSWtNbUVrTVRBa1ZXMXhWbXN3V2tWcVlYcFNMa3hFT0M4M1FXMVFkU0lzSWpFM056TTNNelF5TnpNdU5EWTBNakV3TXlKZCIsImV4cCI6IjIwMjYtMDYtMTdUMDc6NTc6NTNaIiwicHVyIjpudWxsfX0^%^3D--518159f327e5bc0659cb3bf8a06771a3b9d07c0f; _wk_kbc_session=02489b5608a4cade3d082017601ee9a7; _csrf_token=IG8^%^2FLKq5uCTbOYyLbU2XWQE^%^2F9^%^2F^%^2B9wB9hPv9gj4clq0YGSuEpEWaKGU3Cgh1q9iTFKTGjUgSDj^%^2FGzlXYFkOCdEw^%^3D^%^3D^" ^
+  -H ^"Origin: https://kb.cifrium.ru^" ^
+  -H ^"Referer: https://kb.cifrium.ru/lessons/11863/tasks/1167888^" ^
+  -H ^"Sec-Fetch-Dest: empty^" ^
+  -H ^"Sec-Fetch-Mode: cors^" ^
+  -H ^"Sec-Fetch-Site: same-origin^" ^
+  -H ^"User-Agent: Mozilla/5.0 (Windows NT 10.0; Win64; x64) AppleWebKit/537.36 (KHTML, like Gecko) Chrome/145.0.0.0 Safari/537.36^" ^
+  -H ^"X-CSRF-Token: IG8/LKq5uCTbOYyLbU2XWQE/9/+9wB9hPv9gj4clq0YGSuEpEWaKGU3Cgh1q9iTFKTGjUgSDj/GzlXYFkOCdEw==^" ^
+  -H ^"X-Device-Id: fc843a63c432edc43ad8b96dd2c8eae4^" ^
+  -H ^"X-Referer: https://kb.cifrium.ru/lessons/11863/tasks/1167888^" ^
+  -H ^"X-Requested-With: XMLHttpRequest^" ^
+  -H ^"X-Skip-Error-Notification: true^" ^
+  -H ^"sec-ch-ua: ^\^"Not:A-Brand^\^";v=^\^"99^\^", ^\^"Google Chrome^\^";v=^\^"145^\^", ^\^"Chromium^\^";v=^\^"145^\^"^" ^
+  -H ^"sec-ch-ua-mobile: ?0^" ^
+  -H ^"sec-ch-ua-platform: ^\^"Windows^\^"^" ^
+  --data-raw ^"------WebKitFormBoundaryOSVeRHNFQJBW6Cq6^
+Content-Disposition: form-data; name=^\^"questions^[1207775^]^[10162116^]^\^"^
+^
+10162117^
+------WebKitFormBoundaryOSVeRHNFQJBW6Cq6^
+Content-Disposition: form-data; name=^\^"questions^[1207775^]^[10162118^]^\^"^
+^
+10162119^
+------WebKitFormBoundaryOSVeRHNFQJBW6Cq6^
+Content-Disposition: form-data; name=^\^"questions^[1207775^]^[10162120^]^\^"^
+^
+10162121^
+------WebKitFormBoundaryOSVeRHNFQJBW6Cq6^
+Content-Disposition: form-data; name=^\^"questions^[1207775^]^[10162122^]^\^"^
+^
+10162123^
+------WebKitFormBoundaryOSVeRHNFQJBW6Cq6^
+Content-Disposition: form-data; name=^\^"questions^[1207775^]^[10162124^]^\^"^
+^
+10162125^
+------WebKitFormBoundaryOSVeRHNFQJBW6Cq6--^
+^"</t>
   </si>
 </sst>
 </file>
@@ -139,7 +255,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -155,9 +271,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -195,7 +311,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -301,7 +417,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -443,7 +559,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -451,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D00819F-1C48-4D61-BB16-78A968D2A3F3}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="55.42578125" customWidth="1"/>
@@ -677,6 +793,116 @@
         <v>15</v>
       </c>
     </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>11862</v>
+      </c>
+      <c r="B21">
+        <v>1167883</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>11862</v>
+      </c>
+      <c r="B22">
+        <v>1167884</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>11862</v>
+      </c>
+      <c r="B23">
+        <v>1167885</v>
+      </c>
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>11862</v>
+      </c>
+      <c r="B24">
+        <v>1167886</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>11862</v>
+      </c>
+      <c r="B25">
+        <v>1197295</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>11863</v>
+      </c>
+      <c r="B26">
+        <v>1167887</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>11863</v>
+      </c>
+      <c r="B27">
+        <v>1167888</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>11863</v>
+      </c>
+      <c r="B28">
+        <v>1167889</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>11863</v>
+      </c>
+      <c r="B29">
+        <v>1167890</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>11863</v>
+      </c>
+      <c r="B30">
+        <v>1197296</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test2.xlsx
+++ b/test2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4469012-EBF3-448A-8BE8-A2D01F7DC603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30C7063-674E-4F5B-9C1B-9D255CAD2630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6405" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>При вызове указал неправильное количество аргументов</t>
   </si>
@@ -212,6 +212,65 @@
 10162125^
 ------WebKitFormBoundaryOSVeRHNFQJBW6Cq6--^
 ^"</t>
+  </si>
+  <si>
+    <t>design = ["Геймплей", "Нарративная цель", "Нарративный бэкграунд", "Ментальная модель"]
+str = ""
+for i in design:
+  str += i + " "
+print(str.strip(), end="")</t>
+  </si>
+  <si>
+    <t>words = ["сеттинг", "музыка", "персонажи", "игровой движок", "лор"]
+for item in words:
+    if item in ["сеттинг", "персонажи", "лор"]:
+        print(item)</t>
+  </si>
+  <si>
+    <t>script = "*** – это текстовый документ, который описывает сюжет, персонажей, диалоги и общий ход игры. Он непосредственно связан с повествовательной структурой и эмоциональным опытом игрока."
+# Заменяем три звездочки на "Сценарий"
+new_script = script.replace("***", "Сценарий игры")
+print(new_script, end="")</t>
+  </si>
+  <si>
+    <t>ментальное моделирование</t>
+  </si>
+  <si>
+    <t>Сюжет</t>
+  </si>
+  <si>
+    <t>settings = ["стимпанк", "киберпанк", "фэнтези", "научная фантастика"]
+objects = ["волшебный меч", "паровой двигатель", "красный бластер", "кибервизор"]
+setting_index = int(input())
+object_index = int(input())
+if (setting_index == 0 and object_index == 1) or \
+   (setting_index == 1 and object_index == 3) or \
+   (setting_index == 2 and object_index == 0) or \
+   (setting_index == 3 and object_index == 2):
+    print("YES")</t>
+  </si>
+  <si>
+    <t>word = input()
+if "лор" in word and word.endswith("р"):
+    print("Проход открыт")
+else:
+    print("Недоступно")</t>
+  </si>
+  <si>
+    <t>kody = ["веревка", "нож", "арбалет", "спички", "вода"]
+nick = ["нож", "веревка", "вода", "спальник", "рация"]
+set_kody = set(kody)
+set_nick = set(nick)
+# Количество уникальных предметов у обоих игроков
+print(len(set_kody | set_nick))
+# Количество общих предметов
+print(len(set_kody &amp; set_nick))</t>
+  </si>
+  <si>
+    <t>симулятор</t>
+  </si>
+  <si>
+    <t>сеттинг</t>
   </si>
 </sst>
 </file>
@@ -567,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D00819F-1C48-4D61-BB16-78A968D2A3F3}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="55.42578125" customWidth="1"/>
@@ -903,6 +962,116 @@
         <v>23</v>
       </c>
     </row>
+    <row r="31" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>11864</v>
+      </c>
+      <c r="B31">
+        <v>1167896</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>11864</v>
+      </c>
+      <c r="B32">
+        <v>1167897</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>11864</v>
+      </c>
+      <c r="B33">
+        <v>1167898</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>11864</v>
+      </c>
+      <c r="B34">
+        <v>1197297</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>11864</v>
+      </c>
+      <c r="B35">
+        <v>1197298</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>11865</v>
+      </c>
+      <c r="B36">
+        <v>1167899</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>11865</v>
+      </c>
+      <c r="B37">
+        <v>1167900</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>11865</v>
+      </c>
+      <c r="B38">
+        <v>1167901</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>11865</v>
+      </c>
+      <c r="B39">
+        <v>1197299</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>11865</v>
+      </c>
+      <c r="B40">
+        <v>1197300</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test2.xlsx
+++ b/test2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30C7063-674E-4F5B-9C1B-9D255CAD2630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C84AC6C-FC0E-41E2-AD6A-DC006C5380EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6405" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
+    <workbookView xWindow="14310" yWindow="3465" windowWidth="14040" windowHeight="11295" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>При вызове указал неправильное количество аргументов</t>
   </si>
@@ -271,6 +271,107 @@
   </si>
   <si>
     <t>сеттинг</t>
+  </si>
+  <si>
+    <t>participants = int(input())
+avg_hours_per_day = float(input())
+total_beta_hours = participants * avg_hours_per_day * 7
+nick_hours = 5
+result = total_beta_hours / nick_hours
+print(result)</t>
+  </si>
+  <si>
+    <t>name = input()
+time = input()
+day_month = input()
+year = input()
+first_letter = name[0] + "."
+time_without_colon = time.replace(":", "")
+version_code = first_letter + time_without_colon + day_month + year
+print(version_code)</t>
+  </si>
+  <si>
+    <t>form = ["круглый", "шипастый"]
+clothes = ["кузнечный молот", "корона", "дырявые сандалии", "мантия монарха"]
+color = ["тёмно-фиолетовый", "кроваво-красный", "желтый"]
+result = ["желтый", "круглый", "корона", "мантия монарха"]
+result.sort()
+print(result)</t>
+  </si>
+  <si>
+    <t>релиз</t>
+  </si>
+  <si>
+    <t>размер</t>
+  </si>
+  <si>
+    <t>A = {"волшебный меч", "чешуя дракона", "старые сандалии", "чайный сервиз"}
+B = {"15 метров верёвки", "волшебный меч", "эликсир превосходного уклонения", "чайный сервиз", "старые сандалии"}
+from_warrior_to_trader = {"чешуя дракона"}
+from_trader_to_warrior = {"эликсир превосходного уклонения", "15 метров верёвки"}
+traded = from_warrior_to_trader | from_trader_to_warrior
+all_items = A | B
+not_traded = all_items - traded
+result = sorted(list(not_traded))
+print(result)</t>
+  </si>
+  <si>
+    <t>A = "предметы и персонажи, которые дополняют информацию о мире вокруг"
+B = "предметы и персонажи, которые связаны с нарративным дизайном сценария"
+C = "интерактивные элементы интерфейса"
+D = "любые другие объекты, с которыми можно взаимодействовать (содержимое инвентаря игрока, подсказки, мини-игры внутри большой игры и т.д.)"
+interactive_elements = [A, B, C, D]
+interactive_elements.sort()
+print(interactive_elements)</t>
+  </si>
+  <si>
+    <t>L = ["сосновый лес", "дорога", "меню", "кафе", "горы в далеке", "официант"]
+def filter_interactive(items):
+    interactive = [item for item in items if item in ["меню", "официант"]]
+    print(interactive)
+filter_interactive(L)</t>
+  </si>
+  <si>
+    <t>pack</t>
+  </si>
+  <si>
+    <t>Entry</t>
+  </si>
+  <si>
+    <t>Обладает уникальными способностями, которые делают его главным героем -&gt; Протагонист</t>
+  </si>
+  <si>
+    <t>player_level = int(input())
+planet_defense = int(input())
+if player_level &gt; planet_defense:
+    print("Планета захвачена!")
+elif player_level == planet_defense:
+    print("Ничья!")
+else:
+    print("Атака не удалась!")</t>
+  </si>
+  <si>
+    <t>a = [1, 2, 3, 4, 5]
+total_coal = 0
+for i in range(len(a)):
+    coal_in_wagon = a[i] + i
+    total_coal += coal_in_wagon
+print(total_coal)</t>
+  </si>
+  <si>
+    <t>Текст, Схема, Таблица, Изображение</t>
+  </si>
+  <si>
+    <t>Дизайн-документ может подвергаться изменениям в зависимости от потребностей и обратной связи от разработчиков и тестировщиков, Изменения в дизайн-документе должны быть согласованы и задокументированы, чтобы сохранить целостность игрового процесса</t>
+  </si>
+  <si>
+    <t>директория</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>a</t>
   </si>
 </sst>
 </file>
@@ -626,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D00819F-1C48-4D61-BB16-78A968D2A3F3}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="55.42578125" customWidth="1"/>
@@ -1072,6 +1173,215 @@
         <v>35</v>
       </c>
     </row>
+    <row r="41" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>11866</v>
+      </c>
+      <c r="B41">
+        <v>1167902</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>11866</v>
+      </c>
+      <c r="B42">
+        <v>1167903</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>11866</v>
+      </c>
+      <c r="B43">
+        <v>1167904</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>11866</v>
+      </c>
+      <c r="B44">
+        <v>1197301</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>11866</v>
+      </c>
+      <c r="B45">
+        <v>1197302</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="285" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>11867</v>
+      </c>
+      <c r="B46">
+        <v>1167909</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>11867</v>
+      </c>
+      <c r="B47">
+        <v>1167910</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>11867</v>
+      </c>
+      <c r="B48">
+        <v>1167911</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>11867</v>
+      </c>
+      <c r="B49">
+        <v>1197303</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>11867</v>
+      </c>
+      <c r="B50">
+        <v>1197304</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>11868</v>
+      </c>
+      <c r="B51">
+        <v>1167912</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>11868</v>
+      </c>
+      <c r="B52">
+        <v>1167913</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>11868</v>
+      </c>
+      <c r="B53">
+        <v>1167914</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>11869</v>
+      </c>
+      <c r="B54">
+        <v>1167915</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>11869</v>
+      </c>
+      <c r="B55">
+        <v>1167916</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>11869</v>
+      </c>
+      <c r="B56">
+        <v>1167917</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>11869</v>
+      </c>
+      <c r="B57">
+        <v>1167918</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>11869</v>
+      </c>
+      <c r="B58">
+        <v>1167919</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>11869</v>
+      </c>
+      <c r="B59">
+        <v>1167920</v>
+      </c>
+      <c r="C59">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test2.xlsx
+++ b/test2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C84AC6C-FC0E-41E2-AD6A-DC006C5380EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB13123-B1BE-4FAC-869F-5293BEB2F702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14310" yWindow="3465" windowWidth="14040" windowHeight="11295" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
+    <workbookView xWindow="13965" yWindow="3600" windowWidth="14040" windowHeight="11295" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="73">
   <si>
     <t>При вызове указал неправильное количество аргументов</t>
   </si>
@@ -372,6 +372,112 @@
   </si>
   <si>
     <t>a</t>
+  </si>
+  <si>
+    <t>Объект -&gt; Кофеварка
+Атрибут -&gt; Объем воды
+Метод -&gt; Приготовление кофе</t>
+  </si>
+  <si>
+    <t>Метод</t>
+  </si>
+  <si>
+    <t>Атрибут</t>
+  </si>
+  <si>
+    <t>прыжок</t>
+  </si>
+  <si>
+    <t>class Profit:
+    def __init__(self, income, expenses):
+        # Инициализация атрибутов-свойств
+        self.income = income
+        self.expenses = expenses
+    def calculate_revenue(self):
+        # Метод для расчета чистой выручки
+        return self.income - self.expenses
+# 1. Запрашиваем данные (используем float для поддержки дробных чисел)
+income_data = float(input())
+expenses_data = float(input())
+# 2. Создаем экземпляр класса Profit
+project_profit = Profit(income_data, expenses_data)
+# 3. Вызываем метод и 4. Выводим результат
+print(project_profit.calculate_revenue())</t>
+  </si>
+  <si>
+    <t>имеет имя Word и не наследует никакой другой класс.</t>
+  </si>
+  <si>
+    <t>self</t>
+  </si>
+  <si>
+    <t>имеют однотипную реализацию входящих в них методов</t>
+  </si>
+  <si>
+    <t>def F(n):
+    # Базовый случай: если n равно 1, возвращаем 1
+    if n == 1:
+        return 1
+    # Рекурсивный шаг: вычисляем по формуле 2 * F(n-1) + 1
+    else:
+        return 2 * F(n-1) + 1
+# Вычисляем и выводим значение для F(6)
+print(F(6))</t>
+  </si>
+  <si>
+    <t>Во второй строке присутствует лишний аргумент attribute</t>
+  </si>
+  <si>
+    <t>Инкапсуляция</t>
+  </si>
+  <si>
+    <t>Avatar -&gt; имя класса
+class -&gt; инструкция
+prof -&gt; атрибут-свойство
+Name -&gt; атрибут-функция
+"face" -&gt; значение атрибута</t>
+  </si>
+  <si>
+    <t>class Phone:
+    def __init__(self, brand, model):
+        self.brand = brand
+        self.model = model
+    def display_info(self):
+        print(f"Бренд: {self.brand} Модель: {self.model}")
+# Запрашиваем данные у пользователя
+brand = input()
+model = input()
+# Создаем экземпляр класса Phone
+phone = Phone(brand, model)
+# Выводим информацию о телефоне
+phone.display_info()</t>
+  </si>
+  <si>
+    <t>Функция, которая инициализирует переменные класса значениями по умолчанию</t>
+  </si>
+  <si>
+    <t>Использование конструкции def __init__(self):</t>
+  </si>
+  <si>
+    <t>Имя звезды: Сириус, Величина: -1.46</t>
+  </si>
+  <si>
+    <t>Фрукт: яблоко сезон: осень</t>
+  </si>
+  <si>
+    <t>Наследование</t>
+  </si>
+  <si>
+    <t>class Dragon:
+    def __init__(self, name, power_level):
+        self.name = name
+        self.power_level = power_level
+    def display_info(self):
+        print(f"Имя дракона: {self.name}, Уровень мощности: {self.power_level}")
+# Создаем экземпляр класса Dragon для дракона "Фирафлира" с уровнем мощности 5000
+dragon = Dragon("Фирафлира", 5000)
+# Выводим информацию о драконе
+dragon.display_info()</t>
   </si>
 </sst>
 </file>
@@ -727,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D00819F-1C48-4D61-BB16-78A968D2A3F3}">
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="55.42578125" customWidth="1"/>
@@ -1382,6 +1488,336 @@
         <v>8</v>
       </c>
     </row>
+    <row r="60" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>11871</v>
+      </c>
+      <c r="B60">
+        <v>1167922</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>11871</v>
+      </c>
+      <c r="B61">
+        <v>1167923</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>11871</v>
+      </c>
+      <c r="B62">
+        <v>1167924</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>11872</v>
+      </c>
+      <c r="B63">
+        <v>1167925</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>11872</v>
+      </c>
+      <c r="B64">
+        <v>1167926</v>
+      </c>
+      <c r="C64">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>11872</v>
+      </c>
+      <c r="B65">
+        <v>1167927</v>
+      </c>
+      <c r="C65">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="300" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>11873</v>
+      </c>
+      <c r="B66">
+        <v>1167928</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>11873</v>
+      </c>
+      <c r="B67">
+        <v>1167929</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>11873</v>
+      </c>
+      <c r="B68">
+        <v>1167930</v>
+      </c>
+      <c r="C68">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>11873</v>
+      </c>
+      <c r="B69">
+        <v>1167931</v>
+      </c>
+      <c r="C69">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>11873</v>
+      </c>
+      <c r="B70">
+        <v>1167932</v>
+      </c>
+      <c r="C70">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>11873</v>
+      </c>
+      <c r="B71">
+        <v>1167933</v>
+      </c>
+      <c r="C71">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>11874</v>
+      </c>
+      <c r="B72">
+        <v>1167935</v>
+      </c>
+      <c r="C72" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>11874</v>
+      </c>
+      <c r="B73">
+        <v>1167936</v>
+      </c>
+      <c r="C73" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>11874</v>
+      </c>
+      <c r="B74">
+        <v>1167937</v>
+      </c>
+      <c r="C74">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>11874</v>
+      </c>
+      <c r="B75">
+        <v>1167934</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>11875</v>
+      </c>
+      <c r="B76">
+        <v>1167938</v>
+      </c>
+      <c r="C76" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>11875</v>
+      </c>
+      <c r="B77">
+        <v>1167939</v>
+      </c>
+      <c r="C77" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>11875</v>
+      </c>
+      <c r="B78">
+        <v>1167940</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>11876</v>
+      </c>
+      <c r="B79">
+        <v>1167941</v>
+      </c>
+      <c r="C79" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>11876</v>
+      </c>
+      <c r="B80">
+        <v>1167942</v>
+      </c>
+      <c r="C80" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>11876</v>
+      </c>
+      <c r="B81">
+        <v>1167943</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="255" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>11876</v>
+      </c>
+      <c r="B82">
+        <v>1167951</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>11877</v>
+      </c>
+      <c r="B83">
+        <v>1167944</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>11877</v>
+      </c>
+      <c r="B84">
+        <v>1167945</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>11877</v>
+      </c>
+      <c r="B85">
+        <v>1167946</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>11877</v>
+      </c>
+      <c r="B86">
+        <v>1167950</v>
+      </c>
+      <c r="C86">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>11877</v>
+      </c>
+      <c r="B87">
+        <v>1167952</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>11878</v>
+      </c>
+      <c r="B88">
+        <v>1167947</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="225" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>11878</v>
+      </c>
+      <c r="B89">
+        <v>1167949</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test2.xlsx
+++ b/test2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB13123-B1BE-4FAC-869F-5293BEB2F702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5705B164-3F56-4712-BA4C-9FA87E258DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13965" yWindow="3600" windowWidth="14040" windowHeight="11295" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="14040" windowHeight="11295" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
   <si>
     <t>При вызове указал неправильное количество аргументов</t>
   </si>
@@ -478,6 +478,21 @@
 dragon = Dragon("Фирафлира", 5000)
 # Выводим информацию о драконе
 dragon.display_info()</t>
+  </si>
+  <si>
+    <t>Пройти игру</t>
+  </si>
+  <si>
+    <t>Космические</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Экономические</t>
+  </si>
+  <si>
+    <t>Основную игровую механику</t>
   </si>
 </sst>
 </file>
@@ -833,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D00819F-1C48-4D61-BB16-78A968D2A3F3}">
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="55.42578125" customWidth="1"/>
@@ -1818,6 +1833,61 @@
         <v>72</v>
       </c>
     </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>11881</v>
+      </c>
+      <c r="B90">
+        <v>1167953</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>11881</v>
+      </c>
+      <c r="B91">
+        <v>1167954</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>11881</v>
+      </c>
+      <c r="B92">
+        <v>1167955</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>11881</v>
+      </c>
+      <c r="B93">
+        <v>1201478</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>11881</v>
+      </c>
+      <c r="B94">
+        <v>1201479</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test2.xlsx
+++ b/test2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5705B164-3F56-4712-BA4C-9FA87E258DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD3FE33-2E1E-4027-8094-28CB27D15691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="14040" windowHeight="11295" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
+    <workbookView xWindow="12150" yWindow="3420" windowWidth="14040" windowHeight="11295" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="170">
   <si>
     <t>При вызове указал неправильное количество аргументов</t>
   </si>
@@ -494,12 +494,433 @@
   <si>
     <t>Основную игровую механику</t>
   </si>
+  <si>
+    <t>шахматы -&gt; детерминированная игра
+камень/ножницы/бумага -&gt; недетерминированная игра
+крестики-нолики -&gt; детерминированная игра
+мафия -&gt; недетерминированная игра</t>
+  </si>
+  <si>
+    <t>Анализ геймплейных данных и обратная связь от игроков для определения дисбаланса и корректировки игровых параметров, Балансировка игровых уровней, чтобы они были сложными, но не непосильными для игроков., Балансировка игровой экономики, чтобы обеспечить равновесие между доходами и расходами в игре.</t>
+  </si>
+  <si>
+    <t>consumed = int(input())
+norm = int(input())
+if consumed &lt; norm:
+    print("Дефицит")
+elif consumed == norm:
+    print("Норма")
+else:
+    print("Избыток")</t>
+  </si>
+  <si>
+    <t>шахматы</t>
+  </si>
+  <si>
+    <t>Это уровень вовлеченности игрока, при котором он получает удовольствие от игры, не чувствуя ни скуки, ни непреодолимой сложности</t>
+  </si>
+  <si>
+    <t>Внутренняя мотивация связана с внутренними ценностями и удовлетворением от самого процесса выполнения задачи, в то время как внешняя мотивация приводит к выполнению задачи, учитывая внешние поощрения и наказания.</t>
+  </si>
+  <si>
+    <t>Прибор с кнопкой и отверстием, предназначенный для анализа реакции животного на поощрения</t>
+  </si>
+  <si>
+    <t>levels = 5
+for i in range(1, levels + 1):
+    spaces = ' ' * (levels - i)
+    print(spaces + '* ' * i)</t>
+  </si>
+  <si>
+    <t>Карьеристы (Достигатели)</t>
+  </si>
+  <si>
+    <t>Животные не перестают нажимать кнопку, пока получают вознаграждение, и делают это активнее, если вознаграждение непостоянно.</t>
+  </si>
+  <si>
+    <t>Кнопки джойстика -&gt; Элементы управления
+Карта -&gt; Информационные элементы
+Здоровье персонажа -&gt; Информационные элементы
+Клавиши клавиатуры -&gt; Элементы управления</t>
+  </si>
+  <si>
+    <t>UI отвечает за визуальное и функциональное оформление приложения, а UX - за взаимодействие пользователя с продуктом и его удовлетворенность от использования.</t>
+  </si>
+  <si>
+    <t>def analyze_ux(navigation_score, design_score):
+    score_to_text = {
+        1: "Плохо(",
+        2: "Хорошо)",
+        3: "Супер!"
+    }
+    min_score = min(navigation_score, design_score)
+    if navigation_score == design_score:
+        return score_to_text[navigation_score]
+    else:
+        return score_to_text[min_score]
+nav = int(input())
+design = int(input())
+result = analyze_ux(nav, design)
+print(result)</t>
+  </si>
+  <si>
+    <t>Head-Up Display — информация на экране, не требующая отрыва взгляда от основного действия. Понятие пришло из авиации.</t>
+  </si>
+  <si>
+    <t>UX-дизайнер</t>
+  </si>
+  <si>
+    <t>пользовательский путь</t>
+  </si>
+  <si>
+    <t>bits = int(input())
+colors = 2 ** bits
+print(colors)</t>
+  </si>
+  <si>
+    <t>Количество битов, используемых для определения цвета каждого пикселя.</t>
+  </si>
+  <si>
+    <t>Малое потребление памяти, что эффективно для устройств с ограниченными ресурсами.</t>
+  </si>
+  <si>
+    <t>Из каких этапов состоит путь пользователя в нашей игре?, Каких этапов не хватает для того, чтобы пользователю_x000B_было интересно и удобно играть?, Какие части игры необходимо улучшить?</t>
+  </si>
+  <si>
+    <t>Целевая аудитория</t>
+  </si>
+  <si>
+    <t>a = "Играть"
+b = "Выйти из игры"
+c = "Зайти в игру"
+d = "Выиграть или Проиграть"
+user_journey = [c, a, d, b]
+print(user_journey)</t>
+  </si>
+  <si>
+    <t>Пауза / Экран настроек</t>
+  </si>
+  <si>
+    <t>Разработка концепции UI (какие группы элементов нужны и как они связаны).</t>
+  </si>
+  <si>
+    <t>Спрайт – это основная единица, использующаяся при создании двумерных игр., Спрайт – двумерный графический элемент,_x000B_управляемый отдельно внутри системы, состоящей из множества других изображений.</t>
+  </si>
+  <si>
+    <t>Хитбокс – это невидимая область в виде прямоугольника или другой формы, которая определяет границы объекта</t>
+  </si>
+  <si>
+    <t>modules = ["pygame.display", "pygame.image", "pygame.event", "pygame.sprite"]
+assigments = ["обработка событий", "загрузка изображений", "создание объектов", "создание окна"]
+# Сопоставление по смыслу
+mapping = {
+    "pygame.display": "создание окна",
+    "pygame.image": "загрузка изображений",
+    "pygame.event": "обработка событий",
+    "pygame.sprite": "создание объектов"
+}
+result = []
+for i, module in enumerate(modules):
+    assignment = mapping[module]
+    j = assigments.index(assignment)
+    result.append(f"{i} {j}")
+print("\n".join(result), end="")</t>
+  </si>
+  <si>
+    <t>pygame.display</t>
+  </si>
+  <si>
+    <t>pip install pygame</t>
+  </si>
+  <si>
+    <t>Это бесконечный цикл, который продолжается в течение всего времени работы игры и обеспечивает обновление состояния игры, ввод от пользователя и отрисовку графики.</t>
+  </si>
+  <si>
+    <t>Модель, основанная на сочетании красного, зеленого и синего цветов.</t>
+  </si>
+  <si>
+    <t>class RGB:
+    def __init__(self, r, g, b):
+        self.r = r
+        self.g = g
+        self.b = b
+    def ratio(self):
+        print(round(self.r / 255, 2))
+        print(round(self.g / 255, 2))
+        print(round(self.b / 255, 2))
+r = int(input())
+g = int(input())
+b = int(input())
+color = RGB(r, g, b)
+color.ratio()</t>
+  </si>
+  <si>
+    <t>self.image.fill(GREEN)</t>
+  </si>
+  <si>
+    <t>pygame.QUIT</t>
+  </si>
+  <si>
+    <t>Совокупность элементов дизайна, которые позволяют взаимодействовать пользователю с программным обеспечением, игрой, приложением или сайтом.</t>
+  </si>
+  <si>
+    <t>24-битная глубина цвета позволяет использовать большее количество оттенков цвета.</t>
+  </si>
+  <si>
+    <t>row = int(input())
+col = int(input())
+for i in range(3):
+    for j in range(3):
+        if i == row and j == col:
+            print("X", end="")
+        else:
+            print("*", end="")
+    print()</t>
+  </si>
+  <si>
+    <t>К загруженному изображению (pygame.image.load("object.png"))</t>
+  </si>
+  <si>
+    <t>rect.collidepoint(event.pos)</t>
+  </si>
+  <si>
+    <t>a = pygame.mixer.Sound('file.mp3')</t>
+  </si>
+  <si>
+    <t>sound.play_sound()</t>
+  </si>
+  <si>
+    <t>x1 = int(input())
+x2 = int(input())
+y1 = int(input())
+y2 = int(input())
+if abs(x1 - x2) &lt;= 1 and abs(y1 - y2) &lt;= 1:
+    print("YES")
+else:
+    print("NO")</t>
+  </si>
+  <si>
+    <t>pygame.mixer</t>
+  </si>
+  <si>
+    <t>self.active</t>
+  </si>
+  <si>
+    <t>За создание хитбокса</t>
+  </si>
+  <si>
+    <t>Движение на влево по оси X</t>
+  </si>
+  <si>
+    <t>solutions = []
+for x in range(1, 10001):   
+    if x**5 - 15*x**4 + 85*x**3 - 225*x**2 + 274*x - 120 == 0:       
+        solutions.append(x)
+solutions.sort()
+print(solutions)</t>
+  </si>
+  <si>
+    <t>Изменяет изображение объекта (self.image) в зависимости от нажатых клавиш-стрелок (вверх, вниз, влево, вправо).</t>
+  </si>
+  <si>
+    <t>В зависимости от комбинации нажатых стрелок выбирается соответствующее изображение (например, imageC для вверх+вправо, imageA для вниз+влево).</t>
+  </si>
+  <si>
+    <t>Для завершения работы игрового цикла после нажатия на крестик.</t>
+  </si>
+  <si>
+    <t>Группа для главного героя-лягушки и группа для всех падающих грибочков.</t>
+  </si>
+  <si>
+    <t>n = int(input())
+if n == 1 or n == 2 or n == 3:
+    print(1)
+else:
+    p1, p2, p3 = 1, 1, 1
+    for i in range(4, n + 1):
+        p_next = p1 + p2
+        p1, p2, p3 = p2, p3, p_next
+    print(p3)</t>
+  </si>
+  <si>
+    <t>коллизия</t>
+  </si>
+  <si>
+    <t>Грибы (mushroom_group) удаляются из группы при столкновении с лягушкой (frog).</t>
+  </si>
+  <si>
+    <t>В папке images</t>
+  </si>
+  <si>
+    <t>Программа завершит свою работу.</t>
+  </si>
+  <si>
+    <t>n = input()
+m = int(input())
+print(int(n[m - 1]))</t>
+  </si>
+  <si>
+    <t>Sprite</t>
+  </si>
+  <si>
+    <t>from interface import *</t>
+  </si>
+  <si>
+    <t>x = int(input())
+y = int(input())
+z = int(input())
+if z == 2 * x**2 - 2 * y**2:
+    print("YES")
+else:
+    print("NO")</t>
+  </si>
+  <si>
+    <t>get_rect</t>
+  </si>
+  <si>
+    <t>append</t>
+  </si>
+  <si>
+    <t>Отсутствует расширение png после имени файла</t>
+  </si>
+  <si>
+    <t>pygame.sprite.spritecollide(), pygame.sprite.collide_rect()</t>
+  </si>
+  <si>
+    <t>def is_leap_year(year):
+    if year % 400 == 0:
+        return True
+    elif year % 100 == 0:
+        return False
+    elif year % 4 == 0:
+        return True
+    else:
+        return False
+total = 0
+for year in range(0, 2025):
+    if is_leap_year(year):
+        total += year
+print(total)</t>
+  </si>
+  <si>
+    <t>Программа проверяет события PyGame и завершает работу, если пользователь закрывает окно.</t>
+  </si>
+  <si>
+    <t>Она перебирает все события, которые произошли в PyGame (нажатия клавиш, движение мыши, закрытие окна и т.д.).</t>
+  </si>
+  <si>
+    <t>Изменяется уровень здоровья Кукурузомена</t>
+  </si>
+  <si>
+    <t>if event.key == pygame.K_3</t>
+  </si>
+  <si>
+    <t>n = input()
+if len(n) != 2 or n[0] == '0' or int(n) &lt; 10 or int(n) &gt; 99:
+    print("ERROR")
+else:
+    digit1 = int(n[0])
+    digit2 = int(n[1])
+    max_digit = max(digit1, digit2)
+    min_digit = min(digit1, digit2)
+    print(max_digit, min_digit)</t>
+  </si>
+  <si>
+    <t>Задержка в 1 секунду (1000 миллисекунд), чтобы игрок увидел смену фона и состояние персонажа.</t>
+  </si>
+  <si>
+    <t>Временная смена фона на фоне лечения, отображение довольного состояния персонажа, задержка, возврат фона и изменение параметров (здоровье +2, сон -1, еда -1).</t>
+  </si>
+  <si>
+    <t>Будут созданы два объекта кнопок с изображениями и координатами, и они будут отображены на экране.</t>
+  </si>
+  <si>
+    <t>В строке 1 пропущено двоеточие в конце строки, В строке 2 пропущены координаты изображения</t>
+  </si>
+  <si>
+    <t>Чтобы указать, что игра вышла из режима паузы, и основной игровой цикл может продолжить работу.</t>
+  </si>
+  <si>
+    <t>count = 0
+prev = None
+while True:
+    num = int(input())
+    count += 1
+    if prev is not None and num == prev:
+        break
+    prev = num
+print(count)</t>
+  </si>
+  <si>
+    <t>Кнопки сна, здоровья и сытости становятся неактивны, появляются кнопки управления музыкой и выхода в главное меню, игровой таймер останавливается.</t>
+  </si>
+  <si>
+    <t>Графическая область на заднем плане игровой сцены, которая не является основным игровым элементом, но создает атмосферу и обеспечивает глубину и объемность игрового мира</t>
+  </si>
+  <si>
+    <t>меню</t>
+  </si>
+  <si>
+    <t>n = int(input())
+count = 0
+for i in range(1, n + 1):
+    num = int(input())
+    if i % 2 == 0 and num % 2 == 0:
+        count += 1
+print(count)</t>
+  </si>
+  <si>
+    <t>Арт-стиль, цветовая палитра, дизайн персонажей, фон, анимация и эффекты.</t>
+  </si>
+  <si>
+    <t>Рассказывает о характере, мотивациях и роли персонажа ещё до начала игры.</t>
+  </si>
+  <si>
+    <t>Создание игр в ретро-стиле</t>
+  </si>
+  <si>
+    <t>Применение перспективного вида</t>
+  </si>
+  <si>
+    <t>for num in range(100, 1000):
+    digits = str(num)
+    if len(set(digits)) == 3:
+        print(num)</t>
+  </si>
+  <si>
+    <t>Менять свою позицию или состояние, создавая иллюзию движения или изменения в игровом мире.</t>
+  </si>
+  <si>
+    <t>Изображение, которое кажется трёхмерным, но на самом деле является плоским.</t>
+  </si>
+  <si>
+    <t>(0,0,0)</t>
+  </si>
+  <si>
+    <t>Модель цветов, описывающая цвета при помощи оттенка, насыщенности и яркости</t>
+  </si>
+  <si>
+    <t>x1 = int(input())
+y1 = int(input())
+x2 = int(input())
+y2 = int(input())
+if (x1 + y1) % 2 == (x2 + y2) % 2:
+    print("YES")
+else:
+    print("NO")</t>
+  </si>
+  <si>
+    <t>Отсутствие искажений при изменении размеров изображений.</t>
+  </si>
+  <si>
+    <t>Невозможность масштабирования без потерь.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -507,6 +928,11 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri "/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -529,11 +955,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -848,13 +1275,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D00819F-1C48-4D61-BB16-78A968D2A3F3}">
-  <dimension ref="A1:C94"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C187"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="55.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1">
         <v>11858</v>
       </c>
@@ -865,7 +1292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>11858</v>
       </c>
@@ -876,7 +1303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>11858</v>
       </c>
@@ -887,7 +1314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>11858</v>
       </c>
@@ -898,7 +1325,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>11858</v>
       </c>
@@ -909,7 +1336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>11859</v>
       </c>
@@ -920,7 +1347,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>11859</v>
       </c>
@@ -931,7 +1358,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>11859</v>
       </c>
@@ -942,7 +1369,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="150">
       <c r="A9">
         <v>11859</v>
       </c>
@@ -953,7 +1380,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>11859</v>
       </c>
@@ -964,7 +1391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>11860</v>
       </c>
@@ -975,7 +1402,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>11860</v>
       </c>
@@ -986,7 +1413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>11860</v>
       </c>
@@ -997,7 +1424,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="60">
       <c r="A14">
         <v>11860</v>
       </c>
@@ -1008,7 +1435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>11860</v>
       </c>
@@ -1019,7 +1446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>11861</v>
       </c>
@@ -1030,7 +1457,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>11861</v>
       </c>
@@ -1041,7 +1468,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>11861</v>
       </c>
@@ -1052,7 +1479,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="165">
       <c r="A19">
         <v>11861</v>
       </c>
@@ -1063,7 +1490,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>11861</v>
       </c>
@@ -1074,7 +1501,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>11862</v>
       </c>
@@ -1085,7 +1512,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>11862</v>
       </c>
@@ -1096,7 +1523,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>11862</v>
       </c>
@@ -1107,7 +1534,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="150">
       <c r="A24">
         <v>11862</v>
       </c>
@@ -1118,7 +1545,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>11862</v>
       </c>
@@ -1129,7 +1556,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="409.5">
       <c r="A26">
         <v>11863</v>
       </c>
@@ -1140,7 +1567,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="409.5">
       <c r="A27">
         <v>11863</v>
       </c>
@@ -1151,7 +1578,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28">
         <v>11863</v>
       </c>
@@ -1162,7 +1589,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="120">
       <c r="A29">
         <v>11863</v>
       </c>
@@ -1173,7 +1600,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30">
         <v>11863</v>
       </c>
@@ -1184,7 +1611,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="150">
       <c r="A31">
         <v>11864</v>
       </c>
@@ -1195,7 +1622,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="120">
       <c r="A32">
         <v>11864</v>
       </c>
@@ -1206,7 +1633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="90">
       <c r="A33">
         <v>11864</v>
       </c>
@@ -1217,7 +1644,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34">
         <v>11864</v>
       </c>
@@ -1228,7 +1655,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35">
         <v>11864</v>
       </c>
@@ -1239,7 +1666,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="210">
       <c r="A36">
         <v>11865</v>
       </c>
@@ -1250,7 +1677,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="90">
       <c r="A37">
         <v>11865</v>
       </c>
@@ -1261,7 +1688,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="165">
       <c r="A38">
         <v>11865</v>
       </c>
@@ -1272,7 +1699,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39">
         <v>11865</v>
       </c>
@@ -1283,7 +1710,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40">
         <v>11865</v>
       </c>
@@ -1294,7 +1721,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="150">
       <c r="A41">
         <v>11866</v>
       </c>
@@ -1305,7 +1732,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="195">
       <c r="A42">
         <v>11866</v>
       </c>
@@ -1316,7 +1743,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="150">
       <c r="A43">
         <v>11866</v>
       </c>
@@ -1327,7 +1754,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44">
         <v>11866</v>
       </c>
@@ -1338,7 +1765,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45">
         <v>11866</v>
       </c>
@@ -1349,7 +1776,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="285" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="285">
       <c r="A46">
         <v>11867</v>
       </c>
@@ -1360,7 +1787,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="210">
       <c r="A47">
         <v>11867</v>
       </c>
@@ -1371,7 +1798,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="135">
       <c r="A48">
         <v>11867</v>
       </c>
@@ -1382,7 +1809,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49">
         <v>11867</v>
       </c>
@@ -1393,7 +1820,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50">
         <v>11867</v>
       </c>
@@ -1404,7 +1831,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="30">
       <c r="A51">
         <v>11868</v>
       </c>
@@ -1415,7 +1842,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="135">
       <c r="A52">
         <v>11868</v>
       </c>
@@ -1426,7 +1853,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="150">
       <c r="A53">
         <v>11868</v>
       </c>
@@ -1437,7 +1864,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3">
       <c r="A54">
         <v>11869</v>
       </c>
@@ -1448,7 +1875,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="90">
       <c r="A55">
         <v>11869</v>
       </c>
@@ -1459,7 +1886,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56">
         <v>11869</v>
       </c>
@@ -1470,7 +1897,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57">
         <v>11869</v>
       </c>
@@ -1481,7 +1908,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3">
       <c r="A58">
         <v>11869</v>
       </c>
@@ -1492,7 +1919,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="A59">
         <v>11869</v>
       </c>
@@ -1503,7 +1930,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="45">
       <c r="A60">
         <v>11871</v>
       </c>
@@ -1514,7 +1941,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="A61">
         <v>11871</v>
       </c>
@@ -1525,7 +1952,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3">
       <c r="A62">
         <v>11871</v>
       </c>
@@ -1536,7 +1963,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="A63">
         <v>11872</v>
       </c>
@@ -1547,7 +1974,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="A64">
         <v>11872</v>
       </c>
@@ -1558,7 +1985,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3">
       <c r="A65">
         <v>11872</v>
       </c>
@@ -1569,7 +1996,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="300" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="300">
       <c r="A66">
         <v>11873</v>
       </c>
@@ -1580,7 +2007,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3">
       <c r="A67">
         <v>11873</v>
       </c>
@@ -1591,7 +2018,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3">
       <c r="A68">
         <v>11873</v>
       </c>
@@ -1602,7 +2029,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3">
       <c r="A69">
         <v>11873</v>
       </c>
@@ -1613,7 +2040,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3">
       <c r="A70">
         <v>11873</v>
       </c>
@@ -1624,7 +2051,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3">
       <c r="A71">
         <v>11873</v>
       </c>
@@ -1635,7 +2062,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3">
       <c r="A72">
         <v>11874</v>
       </c>
@@ -1646,7 +2073,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3">
       <c r="A73">
         <v>11874</v>
       </c>
@@ -1657,7 +2084,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3">
       <c r="A74">
         <v>11874</v>
       </c>
@@ -1668,7 +2095,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="165">
       <c r="A75">
         <v>11874</v>
       </c>
@@ -1679,7 +2106,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3">
       <c r="A76">
         <v>11875</v>
       </c>
@@ -1690,7 +2117,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3">
       <c r="A77">
         <v>11875</v>
       </c>
@@ -1701,7 +2128,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="75">
       <c r="A78">
         <v>11875</v>
       </c>
@@ -1712,7 +2139,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3">
       <c r="A79">
         <v>11876</v>
       </c>
@@ -1723,7 +2150,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3">
       <c r="A80">
         <v>11876</v>
       </c>
@@ -1734,7 +2161,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="75">
       <c r="A81">
         <v>11876</v>
       </c>
@@ -1745,7 +2172,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="255" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="255">
       <c r="A82">
         <v>11876</v>
       </c>
@@ -1756,7 +2183,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="30">
       <c r="A83">
         <v>11877</v>
       </c>
@@ -1767,7 +2194,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3">
       <c r="A84">
         <v>11877</v>
       </c>
@@ -1778,7 +2205,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3">
       <c r="A85">
         <v>11877</v>
       </c>
@@ -1789,7 +2216,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3">
       <c r="A86">
         <v>11877</v>
       </c>
@@ -1800,7 +2227,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3">
       <c r="A87">
         <v>11877</v>
       </c>
@@ -1811,7 +2238,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3">
       <c r="A88">
         <v>11878</v>
       </c>
@@ -1822,7 +2249,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="225" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="225">
       <c r="A89">
         <v>11878</v>
       </c>
@@ -1833,7 +2260,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3">
       <c r="A90">
         <v>11881</v>
       </c>
@@ -1844,7 +2271,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3">
       <c r="A91">
         <v>11881</v>
       </c>
@@ -1855,7 +2282,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3">
       <c r="A92">
         <v>11881</v>
       </c>
@@ -1866,7 +2293,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3">
       <c r="A93">
         <v>11881</v>
       </c>
@@ -1877,7 +2304,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3">
       <c r="A94">
         <v>11881</v>
       </c>
@@ -1888,7 +2315,1031 @@
         <v>77</v>
       </c>
     </row>
+    <row r="95" spans="1:3" ht="60">
+      <c r="A95">
+        <v>11882</v>
+      </c>
+      <c r="B95">
+        <v>1167956</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="90">
+      <c r="A96">
+        <v>11882</v>
+      </c>
+      <c r="B96">
+        <v>1167957</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="135">
+      <c r="A97">
+        <v>11882</v>
+      </c>
+      <c r="B97">
+        <v>1167958</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98">
+        <v>11882</v>
+      </c>
+      <c r="B98">
+        <v>1201483</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="45">
+      <c r="A99">
+        <v>11882</v>
+      </c>
+      <c r="B99">
+        <v>1201484</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="75">
+      <c r="A100">
+        <v>11883</v>
+      </c>
+      <c r="B100">
+        <v>1167959</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="30">
+      <c r="A101">
+        <v>11883</v>
+      </c>
+      <c r="B101">
+        <v>1167960</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="75">
+      <c r="A102">
+        <v>11883</v>
+      </c>
+      <c r="B102">
+        <v>1167961</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103">
+        <v>11883</v>
+      </c>
+      <c r="B103">
+        <v>1201488</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="45">
+      <c r="A104">
+        <v>11883</v>
+      </c>
+      <c r="B104">
+        <v>1201489</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="60">
+      <c r="A105">
+        <v>11884</v>
+      </c>
+      <c r="B105">
+        <v>1167962</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="60">
+      <c r="A106">
+        <v>11884</v>
+      </c>
+      <c r="B106">
+        <v>1167963</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="300">
+      <c r="A107">
+        <v>11884</v>
+      </c>
+      <c r="B107">
+        <v>1167964</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="45">
+      <c r="A108">
+        <v>11884</v>
+      </c>
+      <c r="B108">
+        <v>1201493</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109">
+        <v>11884</v>
+      </c>
+      <c r="B109">
+        <v>1201494</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110">
+        <v>11885</v>
+      </c>
+      <c r="B110">
+        <v>1167965</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111">
+        <v>11885</v>
+      </c>
+      <c r="B111">
+        <v>1167966</v>
+      </c>
+      <c r="C111">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="75">
+      <c r="A112">
+        <v>11885</v>
+      </c>
+      <c r="B112">
+        <v>1167967</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="30">
+      <c r="A113">
+        <v>11885</v>
+      </c>
+      <c r="B113">
+        <v>1201499</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="30">
+      <c r="A114">
+        <v>11885</v>
+      </c>
+      <c r="B114">
+        <v>1201500</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="60">
+      <c r="A115">
+        <v>11886</v>
+      </c>
+      <c r="B115">
+        <v>1167968</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116">
+        <v>11886</v>
+      </c>
+      <c r="B116">
+        <v>1167969</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="120">
+      <c r="A117">
+        <v>11886</v>
+      </c>
+      <c r="B117">
+        <v>1167970</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118">
+        <v>11886</v>
+      </c>
+      <c r="B118">
+        <v>1201504</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="30">
+      <c r="A119">
+        <v>11886</v>
+      </c>
+      <c r="B119">
+        <v>1201505</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="60">
+      <c r="A120">
+        <v>11887</v>
+      </c>
+      <c r="B120">
+        <v>1167971</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121">
+        <v>11887</v>
+      </c>
+      <c r="B121">
+        <v>1167972</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="300">
+      <c r="A122">
+        <v>11887</v>
+      </c>
+      <c r="B122">
+        <v>1167973</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123">
+        <v>11887</v>
+      </c>
+      <c r="B123">
+        <v>1201510</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124">
+        <v>11887</v>
+      </c>
+      <c r="B124">
+        <v>1201511</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="60">
+      <c r="A125">
+        <v>11888</v>
+      </c>
+      <c r="B125">
+        <v>1167974</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="30">
+      <c r="A126">
+        <v>11888</v>
+      </c>
+      <c r="B126">
+        <v>1167975</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="270">
+      <c r="A127">
+        <v>11888</v>
+      </c>
+      <c r="B127">
+        <v>1167976</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128">
+        <v>11888</v>
+      </c>
+      <c r="B128">
+        <v>1201516</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129">
+        <v>11888</v>
+      </c>
+      <c r="B129">
+        <v>1201517</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="45">
+      <c r="A130">
+        <v>11889</v>
+      </c>
+      <c r="B130">
+        <v>1167977</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="30">
+      <c r="A131">
+        <v>11889</v>
+      </c>
+      <c r="B131">
+        <v>1167978</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="150">
+      <c r="A132">
+        <v>11889</v>
+      </c>
+      <c r="B132">
+        <v>1167979</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="30">
+      <c r="A133">
+        <v>11889</v>
+      </c>
+      <c r="B133">
+        <v>1201521</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134">
+        <v>11889</v>
+      </c>
+      <c r="B134">
+        <v>1201522</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135">
+        <v>11890</v>
+      </c>
+      <c r="B135">
+        <v>1167980</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136">
+        <v>11890</v>
+      </c>
+      <c r="B136">
+        <v>1167981</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="135">
+      <c r="A137">
+        <v>11890</v>
+      </c>
+      <c r="B137">
+        <v>1167982</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138">
+        <v>11890</v>
+      </c>
+      <c r="B138">
+        <v>1201527</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139">
+        <v>11890</v>
+      </c>
+      <c r="B139">
+        <v>1201528</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140">
+        <v>11891</v>
+      </c>
+      <c r="B140">
+        <v>1167983</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141">
+        <v>11891</v>
+      </c>
+      <c r="B141">
+        <v>1167984</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="90">
+      <c r="A142">
+        <v>11891</v>
+      </c>
+      <c r="B142">
+        <v>1167985</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="45">
+      <c r="A143">
+        <v>11891</v>
+      </c>
+      <c r="B143">
+        <v>1201813</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="45">
+      <c r="A144">
+        <v>11891</v>
+      </c>
+      <c r="B144">
+        <v>1201814</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="30">
+      <c r="A145">
+        <v>11892</v>
+      </c>
+      <c r="B145">
+        <v>1167986</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="30">
+      <c r="A146">
+        <v>11892</v>
+      </c>
+      <c r="B146">
+        <v>1167987</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="180">
+      <c r="A147">
+        <v>11892</v>
+      </c>
+      <c r="B147">
+        <v>1167988</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148">
+        <v>11892</v>
+      </c>
+      <c r="B148">
+        <v>1201820</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="30">
+      <c r="A149">
+        <v>11892</v>
+      </c>
+      <c r="B149">
+        <v>1201821</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150">
+        <v>11894</v>
+      </c>
+      <c r="B150">
+        <v>1167989</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151">
+        <v>11894</v>
+      </c>
+      <c r="B151">
+        <v>1167990</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="45">
+      <c r="A152">
+        <v>11894</v>
+      </c>
+      <c r="B152">
+        <v>1167991</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153">
+        <v>11895</v>
+      </c>
+      <c r="B153">
+        <v>1167992</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154">
+        <v>11895</v>
+      </c>
+      <c r="B154">
+        <v>1167993</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="120">
+      <c r="A155">
+        <v>11895</v>
+      </c>
+      <c r="B155">
+        <v>1167994</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156">
+        <v>11895</v>
+      </c>
+      <c r="B156">
+        <v>1201831</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157">
+        <v>11895</v>
+      </c>
+      <c r="B157">
+        <v>1201832</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158">
+        <v>11896</v>
+      </c>
+      <c r="B158">
+        <v>1167995</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159">
+        <v>11896</v>
+      </c>
+      <c r="B159">
+        <v>1167996</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="240">
+      <c r="A160">
+        <v>11896</v>
+      </c>
+      <c r="B160">
+        <v>1167997</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="30">
+      <c r="A161">
+        <v>11896</v>
+      </c>
+      <c r="B161">
+        <v>1201836</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="45">
+      <c r="A162">
+        <v>11896</v>
+      </c>
+      <c r="B162">
+        <v>1201837</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163">
+        <v>11897</v>
+      </c>
+      <c r="B163">
+        <v>1167998</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164">
+        <v>11897</v>
+      </c>
+      <c r="B164">
+        <v>1167999</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="180">
+      <c r="A165">
+        <v>11897</v>
+      </c>
+      <c r="B165">
+        <v>1168000</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="30">
+      <c r="A166">
+        <v>11897</v>
+      </c>
+      <c r="B166">
+        <v>1201848</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="60">
+      <c r="A167">
+        <v>11897</v>
+      </c>
+      <c r="B167">
+        <v>1201852</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="30">
+      <c r="A168">
+        <v>11898</v>
+      </c>
+      <c r="B168">
+        <v>1168001</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="30">
+      <c r="A169">
+        <v>11898</v>
+      </c>
+      <c r="B169">
+        <v>1168002</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="195">
+      <c r="A170">
+        <v>11898</v>
+      </c>
+      <c r="B170">
+        <v>1168003</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="30">
+      <c r="A171">
+        <v>11898</v>
+      </c>
+      <c r="B171">
+        <v>1201866</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="45">
+      <c r="A172">
+        <v>11898</v>
+      </c>
+      <c r="B172">
+        <v>1201866</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="60">
+      <c r="A173">
+        <v>11899</v>
+      </c>
+      <c r="B173">
+        <v>1168004</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174">
+        <v>11899</v>
+      </c>
+      <c r="B174">
+        <v>1168005</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="135">
+      <c r="A175">
+        <v>11899</v>
+      </c>
+      <c r="B175">
+        <v>1168006</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="30">
+      <c r="A176">
+        <v>11899</v>
+      </c>
+      <c r="B176">
+        <v>1201871</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="30">
+      <c r="A177">
+        <v>11899</v>
+      </c>
+      <c r="B177">
+        <v>1201874</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178">
+        <v>11900</v>
+      </c>
+      <c r="B178">
+        <v>1168007</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179">
+        <v>11900</v>
+      </c>
+      <c r="B179">
+        <v>1168008</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="60">
+      <c r="A180">
+        <v>11900</v>
+      </c>
+      <c r="B180">
+        <v>1168009</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="30">
+      <c r="A181">
+        <v>11900</v>
+      </c>
+      <c r="B181">
+        <v>1201881</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="30">
+      <c r="A182">
+        <v>11900</v>
+      </c>
+      <c r="B182">
+        <v>1201886</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183">
+        <v>11901</v>
+      </c>
+      <c r="B183">
+        <v>1168010</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="30">
+      <c r="A184">
+        <v>11901</v>
+      </c>
+      <c r="B184">
+        <v>1168011</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="135">
+      <c r="A185">
+        <v>11901</v>
+      </c>
+      <c r="B185">
+        <v>1168012</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="30">
+      <c r="A186">
+        <v>11901</v>
+      </c>
+      <c r="B186">
+        <v>1201894</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187">
+        <v>11901</v>
+      </c>
+      <c r="B187">
+        <v>1201895</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/test2.xlsx
+++ b/test2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D61D77-0D5F-4BDF-B639-C21699B880D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B2D40C-9A7A-4BDD-956B-0C1A7950CE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Костюм персонажа, Головной убор персонажа</t>
   </si>
@@ -153,6 +153,73 @@
     if ch == max_digit:
         count += 1
 print(count)</t>
+  </si>
+  <si>
+    <t>Разработка функций для кнопок «Уложить спать», «Вылечить» и «Покормить».</t>
+  </si>
+  <si>
+    <t>Открытое тестирование (бета-тест)</t>
+  </si>
+  <si>
+    <t>Некорректно указано имя файла</t>
+  </si>
+  <si>
+    <t>Не является обязательным компонентом компонентом игры</t>
+  </si>
+  <si>
+    <t># Создаем список для подсчета цифр от 1 до 9, изначально все нули
+counts = [0] * 10  # индекс 0..9, но индекс 0 не используем
+while True:
+    num = int(input())
+    if num == 0:
+        break
+    # Если введенная цифра от 1 до 9, увеличиваем счетчик
+    if 1 &lt;= num &lt;= 9:
+        counts[num] += 1
+    # (При желании можно ничего не делать для чисел вне 0-9)
+# Выводим количество от 1 до 9
+print(counts[1:10])</t>
+  </si>
+  <si>
+    <t>Чтобы не увеличивать объем функции play_game и не усложнять структуру игры.</t>
+  </si>
+  <si>
+    <t>В зависимости от глобальной переменной-флага is_music_playing.</t>
+  </si>
+  <si>
+    <t>Отсутствуют скобки справа от update</t>
+  </si>
+  <si>
+    <t>для переключения между главным меню и игрой</t>
+  </si>
+  <si>
+    <t># Вводим три различные цифры
+a = input().strip()
+b = input().strip()
+c = input().strip()
+# Собираем все цифры в список
+digits = [a, b, c]
+# Создаём список для хранения результатов
+numbers = []
+# Тройной вложенный цикл для перебора всех комбинаций (с повторениями)
+for first in digits:          # первая цифра (сотни)
+    if first == '0':          # число не может начинаться с нуля
+        continue
+    for second in digits:     # вторая цифра (десятки)
+        for third in digits:  # третья цифра (единицы)
+            # Составляем трёхзначное число
+            num = first + second + third
+            numbers.append(num)
+# Сортируем результат (лексикографически, как строки)
+numbers.sort()
+# Выводим результат
+print(numbers)</t>
+  </si>
+  <si>
+    <t>return</t>
+  </si>
+  <si>
+    <t>True</t>
   </si>
 </sst>
 </file>
@@ -791,81 +858,168 @@
       <c r="B24">
         <v>1203910</v>
       </c>
-      <c r="C24" s="1"/>
+      <c r="C24" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25">
         <v>11908</v>
       </c>
-      <c r="C25" s="1"/>
+      <c r="B25">
+        <v>1203911</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="C26" s="1"/>
+      <c r="A26">
+        <v>11909</v>
+      </c>
+      <c r="B26">
+        <v>1168028</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="C27" s="1"/>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="C28" s="1"/>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="C29" s="1"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="C30" s="1"/>
+      <c r="A27">
+        <v>11909</v>
+      </c>
+      <c r="B27">
+        <v>1168029</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="240">
+      <c r="A28">
+        <v>11909</v>
+      </c>
+      <c r="B28">
+        <v>1168030</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="30">
+      <c r="A29">
+        <v>11909</v>
+      </c>
+      <c r="B29">
+        <v>1203980</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="30">
+      <c r="A30">
+        <v>11909</v>
+      </c>
+      <c r="B30">
+        <v>1203982</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="C31" s="1"/>
+      <c r="A31">
+        <v>11910</v>
+      </c>
+      <c r="B31">
+        <v>1168031</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="C32" s="2"/>
-    </row>
-    <row r="33" spans="3:3">
-      <c r="C33" s="1"/>
-    </row>
-    <row r="34" spans="3:3">
-      <c r="C34" s="1"/>
-    </row>
-    <row r="35" spans="3:3">
-      <c r="C35" s="1"/>
-    </row>
-    <row r="36" spans="3:3">
+      <c r="A32">
+        <v>11910</v>
+      </c>
+      <c r="B32">
+        <v>1168032</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="405">
+      <c r="A33">
+        <v>11910</v>
+      </c>
+      <c r="B33">
+        <v>1168033</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
+        <v>11910</v>
+      </c>
+      <c r="B34">
+        <v>1203989</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>11910</v>
+      </c>
+      <c r="B35">
+        <v>1203991</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="3:3">
+    <row r="37" spans="1:3">
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="3:3">
+    <row r="38" spans="1:3">
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="3:3">
+    <row r="39" spans="1:3">
       <c r="C39" s="1"/>
     </row>
-    <row r="40" spans="3:3">
+    <row r="40" spans="1:3">
       <c r="C40" s="1"/>
     </row>
-    <row r="41" spans="3:3">
+    <row r="41" spans="1:3">
       <c r="C41" s="1"/>
     </row>
-    <row r="42" spans="3:3">
+    <row r="42" spans="1:3">
       <c r="C42" s="1"/>
     </row>
-    <row r="43" spans="3:3">
+    <row r="43" spans="1:3">
       <c r="C43" s="1"/>
     </row>
-    <row r="44" spans="3:3">
+    <row r="44" spans="1:3">
       <c r="C44" s="1"/>
     </row>
-    <row r="45" spans="3:3">
+    <row r="45" spans="1:3">
       <c r="C45" s="1"/>
     </row>
-    <row r="46" spans="3:3">
+    <row r="46" spans="1:3">
       <c r="C46" s="1"/>
     </row>
-    <row r="47" spans="3:3">
+    <row r="47" spans="1:3">
       <c r="C47" s="1"/>
     </row>
-    <row r="48" spans="3:3">
+    <row r="48" spans="1:3">
       <c r="C48" s="1"/>
     </row>
     <row r="49" spans="3:3">

--- a/test2.xlsx
+++ b/test2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B2D40C-9A7A-4BDD-956B-0C1A7950CE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2744DD-8DF9-4EC3-B8C2-E4913B1BFC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
   </bookViews>

--- a/test2.xlsx
+++ b/test2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2744DD-8DF9-4EC3-B8C2-E4913B1BFC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55C2A38-2566-48C1-8AB6-6554919E9006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="90">
   <si>
     <t>Костюм персонажа, Головной убор персонажа</t>
   </si>
@@ -220,6 +220,250 @@
   </si>
   <si>
     <t>True</t>
+  </si>
+  <si>
+    <t>button_init</t>
+  </si>
+  <si>
+    <t>Объект меняет направление движения по оси X при столкновении с другим спрайтом</t>
+  </si>
+  <si>
+    <t>n = int(input())
+if n == 0:
+    print(0)
+else:
+    print(1 + (n - 1) % 9)</t>
+  </si>
+  <si>
+    <t>restart_game</t>
+  </si>
+  <si>
+    <t>Фон и две кнопки (\"Да\" и \"Нет\").</t>
+  </si>
+  <si>
+    <t>restart_game(dis)</t>
+  </si>
+  <si>
+    <t>Так как выход из функции автоматически вызовет завершение цикла.</t>
+  </si>
+  <si>
+    <t># Функция, удаляющая из списка элементы, равные заданному числу
+def remove_element(lst, n):
+    # Создаем новый список, содержащий только элементы, не равные n
+    result = [x for x in lst if x != n]
+    # Выводим результат
+    print(result)
+# Считываем список чисел
+L = list(map(int, input().split()))
+# Считываем число N
+N = int(input())
+# Вызываем функцию
+remove_element(L, N)</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>Чтобы сделать вектор единичным (длиной 1), сохранив направление, но не влияя на итоговую скорость.</t>
+  </si>
+  <si>
+    <t>exit_menu.png</t>
+  </si>
+  <si>
+    <t>Хранение переменных, отвечающих за игровые фоны.</t>
+  </si>
+  <si>
+    <t>N = int(input())
+# Верхняя граница
+print('*' * (N - 1) + '*')
+# Средние строки
+for _ in range(N - 2):
+    print('*' + ' ' * (N - 2) + '*')
+# Нижняя граница (если N &gt; 1)
+if N &gt; 1:
+    print('*' * (N - 1) + '*')</t>
+  </si>
+  <si>
+    <t>4 (нейтральный, для сна, для лечения, для приема пищи)</t>
+  </si>
+  <si>
+    <t>Фон для лечения и фон для сна.</t>
+  </si>
+  <si>
+    <t>Sound загружает файл целиком, а music потоком.</t>
+  </si>
+  <si>
+    <t>Это каналы – это независимые друг от друга аудиосигналы, которые могут воспроизводиться или записываться одновременно.</t>
+  </si>
+  <si>
+    <t>numbers = list(map(int, input().split()))
+# Множество для хранения уже встреченных чисел
+seen = set()
+# Проходим по каждому числу в списке
+for num in numbers:
+    if num in seen:
+        print("YES")
+    else:
+        print("NO")
+        seen.add(num)</t>
+  </si>
+  <si>
+    <t>fade_ms</t>
+  </si>
+  <si>
+    <t>loops</t>
+  </si>
+  <si>
+    <t>чиптюн</t>
+  </si>
+  <si>
+    <t>wav</t>
+  </si>
+  <si>
+    <t># Считываем строку
+s = input()
+# Разбиваем строку по пробелам и собираем обратно с одним пробелом
+result = ' '.join(s.split())
+# Выводим результат
+print(result)</t>
+  </si>
+  <si>
+    <t>Файл, состоящий из информации об амплитуде и частоте звука</t>
+  </si>
+  <si>
+    <t>Саундтрек - это музыкальное сопровождение к фильму или игре</t>
+  </si>
+  <si>
+    <t>Схема, объясняющая, какая часть саундтрека соответствует той или иной части игрового процесса.</t>
+  </si>
+  <si>
+    <t># Считываем начальную длину трека и целевую длину
+x = int(input())
+y = int(input())
+# Начинаем с первого дня
+day = 1
+current_length = x
+# Увеличиваем длину, пока она не достигнет y
+while current_length &lt; y:
+    current_length *= 1.1
+    day += 1
+# Выводим номер дня
+print(day)</t>
+  </si>
+  <si>
+    <t>«Плавание на корабле»</t>
+  </si>
+  <si>
+    <t>Проанализировать сюжет и тему игры, чтобы выбрать стиль саундтрека</t>
+  </si>
+  <si>
+    <t>выбор музыкальной программы, создание музыкального сценария</t>
+  </si>
+  <si>
+    <t>Басовый инструмент держит определенный темп при исполнении музыки.</t>
+  </si>
+  <si>
+    <t>s = "БасЛидПэдами"  # "БасЛидПэдами"
+# Удаляем все буквы 'а'
+s = s.replace('а', '')
+# Сортируем в обратном алфавитном порядке (по убыванию кодов символов)
+result = ''.join(sorted(s, reverse=True))
+print(result)</t>
+  </si>
+  <si>
+    <t>Изменять тон, скорость и громкость, добавлять эффекты</t>
+  </si>
+  <si>
+    <t>Просмотреть руководство и документацию.</t>
+  </si>
+  <si>
+    <t>Звуки, которые служат для создания атмосферы или обстановки в игре.</t>
+  </si>
+  <si>
+    <t>Звуки, которые используются для подчеркивания действий персонажей или событий в игре.</t>
+  </si>
+  <si>
+    <t>Чтобы подчеркнуть события, действия и эмоции в игре.</t>
+  </si>
+  <si>
+    <t>Звуки от взаимодействия персонажа с предметом.</t>
+  </si>
+  <si>
+    <t>Выгружает текущий музыкальный файл из памяти.</t>
+  </si>
+  <si>
+    <t># Класс лягушки
+class Frog:
+    def sound(self):
+        return "Ква-Ква"
+# Класс воробья
+class Sparrow:
+    def sound(self):
+        return "Чирик-Чирик"
+# Класс ёжика
+class Hedgehog:
+    def sound(self):
+        return "Фыр-Фыр"
+# Создаём объекты
+frog = Frog()
+sparrow = Sparrow()
+hedgehog = Hedgehog()
+# Выводим звуки в заданном порядке: лягушка, воробей, ёжик
+print(frog.sound())
+print(sparrow.sound())
+print(hedgehog.sound())</t>
+  </si>
+  <si>
+    <t>Звуки, исходящие от окружающей среды и не зависящие от действий игрока.</t>
+  </si>
+  <si>
+    <t>Звуки, генерируемые самим игроком или движениями персонажей.</t>
+  </si>
+  <si>
+    <t>st2.mp3</t>
+  </si>
+  <si>
+    <t>audiofiles.py</t>
+  </si>
+  <si>
+    <t># Считываем строку с двоичным числом
+binary_string = input()
+# Преобразуем из двоичной в десятичную систему
+decimal_number = int(binary_string, 2)
+# Выводим результат
+print(decimal_number)</t>
+  </si>
+  <si>
+    <t>st1.mp3</t>
+  </si>
+  <si>
+    <t>3D-реализм</t>
+  </si>
+  <si>
+    <t>Первые десятилетия двухтысячных годов</t>
+  </si>
+  <si>
+    <t>Это организация, которая поддерживает и развивает новые проекты, выбранные на конкурсной основе.</t>
+  </si>
+  <si>
+    <t>s = input()
+# Используем множество, чтобы найти символ, который встречается больше 1 раза
+for ch in s:
+    if s.count(ch) &gt; 1:
+        print(ch)
+        break</t>
+  </si>
+  <si>
+    <t>Разработка и публикация собственных игровых проектов.</t>
+  </si>
+  <si>
+    <t>Частые изменения и нестабильность индустрии.</t>
+  </si>
+  <si>
+    <t>Это план, который помогает достичь победы в игре.</t>
+  </si>
+  <si>
+    <t>Это план достижения успеха в игре, включающий в себя тактику, планирование и анализ.</t>
   </si>
 </sst>
 </file>
@@ -984,187 +1228,675 @@
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="C36" s="1"/>
+      <c r="A36">
+        <v>11911</v>
+      </c>
+      <c r="B36">
+        <v>1168034</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="C37" s="1"/>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="C38" s="1"/>
+      <c r="A37">
+        <v>11911</v>
+      </c>
+      <c r="B37">
+        <v>1168035</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="75">
+      <c r="A38">
+        <v>11911</v>
+      </c>
+      <c r="B38">
+        <v>1168036</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="C39" s="1"/>
+      <c r="A39">
+        <v>11911</v>
+      </c>
+      <c r="B39">
+        <v>1204002</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="C40" s="1"/>
+      <c r="A40">
+        <v>11911</v>
+      </c>
+      <c r="B40">
+        <v>1204004</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="C41" s="1"/>
+      <c r="A41">
+        <v>11912</v>
+      </c>
+      <c r="B41">
+        <v>1168037</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="C42" s="1"/>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="C43" s="1"/>
+      <c r="A42">
+        <v>11912</v>
+      </c>
+      <c r="B42">
+        <v>1168038</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="255">
+      <c r="A43">
+        <v>11912</v>
+      </c>
+      <c r="B43">
+        <v>1168039</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="C44" s="1"/>
+      <c r="A44">
+        <v>11912</v>
+      </c>
+      <c r="B44">
+        <v>1204012</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="C45" s="1"/>
+      <c r="A45">
+        <v>11912</v>
+      </c>
+      <c r="B45">
+        <v>1204013</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="C46" s="1"/>
+      <c r="A46">
+        <v>11914</v>
+      </c>
+      <c r="B46">
+        <v>1168040</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="C47" s="1"/>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="C48" s="1"/>
-    </row>
-    <row r="49" spans="3:3">
-      <c r="C49" s="1"/>
-    </row>
-    <row r="50" spans="3:3">
-      <c r="C50" s="1"/>
-    </row>
-    <row r="51" spans="3:3">
-      <c r="C51" s="1"/>
-    </row>
-    <row r="52" spans="3:3">
-      <c r="C52" s="1"/>
-    </row>
-    <row r="53" spans="3:3">
-      <c r="C53" s="1"/>
-    </row>
-    <row r="54" spans="3:3">
-      <c r="C54" s="1"/>
-    </row>
-    <row r="55" spans="3:3">
-      <c r="C55" s="1"/>
-    </row>
-    <row r="56" spans="3:3">
-      <c r="C56" s="1"/>
-    </row>
-    <row r="57" spans="3:3">
-      <c r="C57" s="1"/>
-    </row>
-    <row r="58" spans="3:3">
-      <c r="C58" s="1"/>
-    </row>
-    <row r="59" spans="3:3">
-      <c r="C59" s="1"/>
-    </row>
-    <row r="60" spans="3:3">
-      <c r="C60" s="1"/>
-    </row>
-    <row r="61" spans="3:3">
-      <c r="C61" s="1"/>
-    </row>
-    <row r="62" spans="3:3">
-      <c r="C62" s="1"/>
-    </row>
-    <row r="63" spans="3:3">
-      <c r="C63" s="1"/>
-    </row>
-    <row r="64" spans="3:3">
-      <c r="C64" s="1"/>
-    </row>
-    <row r="65" spans="3:3">
-      <c r="C65" s="1"/>
-    </row>
-    <row r="66" spans="3:3">
-      <c r="C66" s="1"/>
-    </row>
-    <row r="67" spans="3:3">
-      <c r="C67" s="1"/>
-    </row>
-    <row r="68" spans="3:3">
-      <c r="C68" s="1"/>
-    </row>
-    <row r="69" spans="3:3">
-      <c r="C69" s="1"/>
-    </row>
-    <row r="70" spans="3:3">
-      <c r="C70" s="1"/>
-    </row>
-    <row r="71" spans="3:3">
-      <c r="C71" s="1"/>
-    </row>
-    <row r="72" spans="3:3">
-      <c r="C72" s="1"/>
-    </row>
-    <row r="73" spans="3:3">
-      <c r="C73" s="1"/>
-    </row>
-    <row r="74" spans="3:3">
-      <c r="C74" s="1"/>
-    </row>
-    <row r="75" spans="3:3">
-      <c r="C75" s="1"/>
-    </row>
-    <row r="76" spans="3:3">
-      <c r="C76" s="1"/>
-    </row>
-    <row r="77" spans="3:3">
-      <c r="C77" s="1"/>
-    </row>
-    <row r="78" spans="3:3">
-      <c r="C78" s="1"/>
-    </row>
-    <row r="79" spans="3:3">
-      <c r="C79" s="1"/>
-    </row>
-    <row r="80" spans="3:3">
-      <c r="C80" s="1"/>
-    </row>
-    <row r="81" spans="3:3">
-      <c r="C81" s="1"/>
-    </row>
-    <row r="82" spans="3:3">
-      <c r="C82" s="1"/>
-    </row>
-    <row r="83" spans="3:3">
-      <c r="C83" s="1"/>
-    </row>
-    <row r="84" spans="3:3">
-      <c r="C84" s="1"/>
-    </row>
-    <row r="85" spans="3:3">
-      <c r="C85" s="1"/>
-    </row>
-    <row r="86" spans="3:3">
-      <c r="C86" s="1"/>
-    </row>
-    <row r="87" spans="3:3">
-      <c r="C87" s="1"/>
-    </row>
-    <row r="88" spans="3:3">
-      <c r="C88" s="1"/>
-    </row>
-    <row r="89" spans="3:3">
-      <c r="C89" s="1"/>
-    </row>
-    <row r="90" spans="3:3">
-      <c r="C90" s="1"/>
-    </row>
-    <row r="91" spans="3:3">
-      <c r="C91" s="1"/>
-    </row>
-    <row r="92" spans="3:3">
-      <c r="C92" s="1"/>
-    </row>
-    <row r="93" spans="3:3">
-      <c r="C93" s="1"/>
-    </row>
-    <row r="94" spans="3:3">
-      <c r="C94" s="1"/>
-    </row>
-    <row r="95" spans="3:3">
-      <c r="C95" s="1"/>
-    </row>
-    <row r="96" spans="3:3">
-      <c r="C96" s="1"/>
+      <c r="A47">
+        <v>11914</v>
+      </c>
+      <c r="B47">
+        <v>1168041</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="180">
+      <c r="A48">
+        <v>11914</v>
+      </c>
+      <c r="B48">
+        <v>1168042</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
+        <v>11914</v>
+      </c>
+      <c r="B49">
+        <v>1204021</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
+        <v>11914</v>
+      </c>
+      <c r="B50">
+        <v>1204022</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
+        <v>11915</v>
+      </c>
+      <c r="B51">
+        <v>1168043</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
+        <v>11915</v>
+      </c>
+      <c r="B52">
+        <v>1168044</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="180">
+      <c r="A53">
+        <v>11915</v>
+      </c>
+      <c r="B53">
+        <v>1168045</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
+        <v>11915</v>
+      </c>
+      <c r="B54">
+        <v>1205627</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
+        <v>11915</v>
+      </c>
+      <c r="B55">
+        <v>1205619</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
+        <v>11916</v>
+      </c>
+      <c r="B56">
+        <v>1168046</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
+        <v>11916</v>
+      </c>
+      <c r="B57">
+        <v>1168047</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="135">
+      <c r="A58">
+        <v>11916</v>
+      </c>
+      <c r="B58">
+        <v>1168048</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
+        <v>11916</v>
+      </c>
+      <c r="B59">
+        <v>1205633</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
+        <v>11916</v>
+      </c>
+      <c r="B60">
+        <v>1205634</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
+        <v>11917</v>
+      </c>
+      <c r="B61">
+        <v>1168049</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
+        <v>11917</v>
+      </c>
+      <c r="B62">
+        <v>1168050</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="225">
+      <c r="A63">
+        <v>11917</v>
+      </c>
+      <c r="B63">
+        <v>1168051</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
+        <v>11917</v>
+      </c>
+      <c r="B64">
+        <v>1205638</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
+        <v>11917</v>
+      </c>
+      <c r="B65">
+        <v>1205639</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
+        <v>11918</v>
+      </c>
+      <c r="B66">
+        <v>1168052</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
+        <v>11918</v>
+      </c>
+      <c r="B67">
+        <v>1168053</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="150">
+      <c r="A68">
+        <v>11918</v>
+      </c>
+      <c r="B68">
+        <v>1168054</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
+        <v>11918</v>
+      </c>
+      <c r="B69">
+        <v>1205645</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
+        <v>11918</v>
+      </c>
+      <c r="B70">
+        <v>1205646</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
+        <v>11919</v>
+      </c>
+      <c r="B71">
+        <v>1168055</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72">
+        <v>11919</v>
+      </c>
+      <c r="B72">
+        <v>1168056</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
+        <v>11919</v>
+      </c>
+      <c r="B73">
+        <v>1168057</v>
+      </c>
+      <c r="C73" s="1">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
+        <v>11919</v>
+      </c>
+      <c r="B74">
+        <v>1205651</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75">
+        <v>11919</v>
+      </c>
+      <c r="B75">
+        <v>1205653</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <v>11920</v>
+      </c>
+      <c r="B76">
+        <v>1168058</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
+        <v>11920</v>
+      </c>
+      <c r="B77">
+        <v>1168059</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="375">
+      <c r="A78">
+        <v>11920</v>
+      </c>
+      <c r="B78">
+        <v>1168060</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
+        <v>11920</v>
+      </c>
+      <c r="B79">
+        <v>1205657</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
+        <v>11920</v>
+      </c>
+      <c r="B80">
+        <v>1205658</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81">
+        <v>11921</v>
+      </c>
+      <c r="B81">
+        <v>1168061</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82">
+        <v>11921</v>
+      </c>
+      <c r="B82">
+        <v>1168062</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="120">
+      <c r="A83">
+        <v>11921</v>
+      </c>
+      <c r="B83">
+        <v>1168063</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84">
+        <v>11921</v>
+      </c>
+      <c r="B84">
+        <v>1205663</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85">
+        <v>11921</v>
+      </c>
+      <c r="B85">
+        <v>1205664</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86">
+        <v>11922</v>
+      </c>
+      <c r="B86">
+        <v>1168064</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87">
+        <v>11922</v>
+      </c>
+      <c r="B87">
+        <v>1168065</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="120">
+      <c r="A88">
+        <v>11922</v>
+      </c>
+      <c r="B88">
+        <v>1168066</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89">
+        <v>11922</v>
+      </c>
+      <c r="B89">
+        <v>1205668</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90">
+        <v>11922</v>
+      </c>
+      <c r="B90">
+        <v>1205669</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91">
+        <v>11923</v>
+      </c>
+      <c r="B91">
+        <v>1168067</v>
+      </c>
+      <c r="C91" s="1">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92">
+        <v>11923</v>
+      </c>
+      <c r="B92">
+        <v>1168068</v>
+      </c>
+      <c r="C92" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93">
+        <v>11923</v>
+      </c>
+      <c r="B93">
+        <v>1168069</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94">
+        <v>11924</v>
+      </c>
+      <c r="B94">
+        <v>1168070</v>
+      </c>
+      <c r="C94" s="1">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95">
+        <v>11924</v>
+      </c>
+      <c r="B95">
+        <v>1168071</v>
+      </c>
+      <c r="C95" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96">
+        <v>11924</v>
+      </c>
+      <c r="B96">
+        <v>1168072</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="97" spans="3:3">
       <c r="C97" s="1"/>

--- a/test2.xlsx
+++ b/test2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maga\Documents\GitHub\effective-rotary-phone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55C2A38-2566-48C1-8AB6-6554919E9006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C3A5E1-D1D3-40C5-B3D6-65380B2261C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
+    <workbookView xWindow="8550" yWindow="3045" windowWidth="14040" windowHeight="11295" xr2:uid="{FB77B88B-565B-42C3-9C84-2D4FF31A02FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1095,7 +1095,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" ht="30">
       <c r="A24">
         <v>11908</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" ht="30">
       <c r="A27">
         <v>11909</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" ht="30">
       <c r="A37">
         <v>11911</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" ht="30">
       <c r="A42">
         <v>11912</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" ht="30">
       <c r="A45">
         <v>11912</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" ht="45">
       <c r="A52">
         <v>11915</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" ht="30">
       <c r="A60">
         <v>11916</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" ht="30">
       <c r="A61">
         <v>11917</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" ht="30">
       <c r="A62">
         <v>11917</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" ht="30">
       <c r="A65">
         <v>11917</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" ht="30">
       <c r="A66">
         <v>11918</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" ht="30">
       <c r="A67">
         <v>11918</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" ht="30">
       <c r="A71">
         <v>11919</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" ht="30">
       <c r="A72">
         <v>11919</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" ht="30">
       <c r="A79">
         <v>11920</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" ht="30">
       <c r="A80">
         <v>11920</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" ht="30">
       <c r="A87">
         <v>11922</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" ht="30">
       <c r="A96">
         <v>11924</v>
       </c>
